--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484329_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484329_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6575</v>
+        <v>10.3875</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5595</v>
+        <v>6.3167</v>
       </c>
       <c r="F2" t="n">
-        <v>4.098</v>
+        <v>4.0707</v>
       </c>
       <c r="G2" t="n">
         <v>8.1638</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7357</v>
+        <v>0.4656</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5009</v>
+        <v>0.2581</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2348</v>
+        <v>0.2075</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.3295</v>
+        <v>8.41</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0336</v>
+        <v>4.2852</v>
       </c>
       <c r="F3" t="n">
-        <v>5.296</v>
+        <v>4.1248</v>
       </c>
       <c r="G3" t="n">
         <v>4.722</v>
@@ -688,13 +688,13 @@
         <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0681</v>
+        <v>1.1486</v>
       </c>
       <c r="T3" t="n">
-        <v>1.175</v>
+        <v>0.4266</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8931</v>
+        <v>0.722</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2924</v>
+        <v>5.4928</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6429</v>
+        <v>4.0068</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6495</v>
+        <v>1.4861</v>
       </c>
       <c r="G4" t="n">
         <v>3.1185</v>
@@ -766,13 +766,13 @@
         <v>2.7348</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8381</v>
+        <v>-0.6377</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.3624</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1119</v>
+        <v>-0.2753</v>
       </c>
       <c r="V4" t="n">
         <v>0.2772</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5251</v>
+        <v>4.6479</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5236</v>
+        <v>2.483</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0014</v>
+        <v>2.1648</v>
       </c>
       <c r="G5" t="n">
         <v>4.0413</v>
@@ -844,13 +844,13 @@
         <v>2.3441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1832</v>
+        <v>0.3061</v>
       </c>
       <c r="T5" t="n">
-        <v>0.311</v>
+        <v>0.2704</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1277</v>
+        <v>0.0357</v>
       </c>
       <c r="V5" t="n">
         <v>0.8865</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9485</v>
+        <v>4.2814</v>
       </c>
       <c r="E6" t="n">
-        <v>2.71</v>
+        <v>2.7706</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2385</v>
+        <v>1.5109</v>
       </c>
       <c r="G6" t="n">
         <v>3.3513</v>
@@ -922,13 +922,13 @@
         <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7814</v>
+        <v>-0.4485</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1732</v>
+        <v>-0.1127</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6082</v>
+        <v>-0.3358</v>
       </c>
       <c r="V6" t="n">
         <v>2.16</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6307</v>
+        <v>3.2917</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8697</v>
+        <v>2.6254</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.239</v>
+        <v>0.6663</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5783</v>
+        <v>2.2635</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7455</v>
+        <v>0.3888</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8328</v>
+        <v>1.8746</v>
       </c>
       <c r="J7" t="n">
-        <v>5.4771</v>
+        <v>2.2781</v>
       </c>
       <c r="K7" t="n">
-        <v>2.374</v>
+        <v>0.9427</v>
       </c>
       <c r="L7" t="n">
-        <v>3.103</v>
+        <v>1.3354</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8988</v>
+        <v>-0.0146</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.5538</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2702</v>
+        <v>0.5393</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1745</v>
+        <v>-0.3625</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0689</v>
+        <v>-0.262</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2433</v>
+        <v>-0.1005</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1638</v>
+        <v>0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.441</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.1089</v>
+        <v>3.279</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5242</v>
+        <v>3.6269</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5846</v>
+        <v>-0.348</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2635</v>
+        <v>4.5783</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3888</v>
+        <v>1.7455</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8746</v>
+        <v>2.8328</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2781</v>
+        <v>5.4771</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9427</v>
+        <v>2.374</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3354</v>
+        <v>3.103</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0146</v>
+        <v>-0.8988</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5538</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5393</v>
+        <v>-0.2702</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5453</v>
+        <v>-0.5262</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3631</v>
+        <v>-0.1739</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1822</v>
+        <v>-0.3523</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6093</v>
+        <v>-1.1638</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.441</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6869</v>
+        <v>3.2492</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6823</v>
+        <v>-1.4195</v>
       </c>
       <c r="F9" t="n">
-        <v>4.3691</v>
+        <v>4.6687</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2223</v>
@@ -1156,13 +1156,13 @@
         <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3725</v>
+        <v>0.1898</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0522</v>
+        <v>0.2106</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3204</v>
+        <v>-0.0208</v>
       </c>
       <c r="V9" t="n">
         <v>1.3283</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7177</v>
+        <v>1.9181</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004</v>
+        <v>0.3679</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7137</v>
+        <v>1.5502</v>
       </c>
       <c r="G10" t="n">
         <v>1.0379</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.629</v>
+        <v>-0.4286</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4842</v>
+        <v>-0.1203</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1448</v>
+        <v>-0.3083</v>
       </c>
       <c r="V10" t="n">
         <v>0.3321</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1389</v>
+        <v>1.4247</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5666</v>
+        <v>-1.7983</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7055</v>
+        <v>3.223</v>
       </c>
       <c r="G11" t="n">
         <v>0.6806</v>
@@ -1312,13 +1312,13 @@
         <v>2.5395</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4599</v>
+        <v>-0.1741</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6125</v>
+        <v>-0.0951</v>
       </c>
       <c r="V11" t="n">
         <v>0.3321</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1661</v>
+        <v>-1.0378</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4884</v>
+        <v>-0.3873</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6777</v>
+        <v>-0.6505</v>
       </c>
       <c r="G12" t="n">
         <v>-0.614</v>
@@ -1390,13 +1390,13 @@
         <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1029</v>
+        <v>0.0255</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V12" t="n">
         <v>0.3321</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3174</v>
+        <v>-1.1867</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3792</v>
+        <v>-0.5209</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9382</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>1.6669</v>
@@ -1468,13 +1468,13 @@
         <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7071</v>
+        <v>-0.5764</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1899</v>
+        <v>0.0482</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.897</v>
+        <v>-0.6246</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4959</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>43.55260000000001</v>
+        <v>44.1578</v>
       </c>
       <c r="E14" t="n">
-        <v>21.751</v>
+        <v>22.3565</v>
       </c>
       <c r="F14" t="n">
-        <v>21.8014</v>
+        <v>21.8012</v>
       </c>
       <c r="G14" t="n">
         <v>32.7878</v>
@@ -1546,13 +1546,13 @@
         <v>24.4179</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6237</v>
+        <v>-1.0184</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5216000000000001</v>
+        <v>0.08369999999999997</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1019</v>
+        <v>-1.1021</v>
       </c>
       <c r="V14" t="n">
         <v>3.597899999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4392</v>
+        <v>0.7037</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8788</v>
+        <v>2.9799</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4396</v>
+        <v>-2.2762</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9192</v>
@@ -1624,13 +1624,13 @@
         <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2383</v>
+        <v>0.5029</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4679</v>
+        <v>0.569</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2296</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.7061</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.201</v>
+        <v>-1.5982</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4009</v>
+        <v>0.3625</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.602</v>
+        <v>-1.9607</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0004</v>
+        <v>-0.2277</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1497</v>
+        <v>0.9872</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8508</v>
+        <v>-1.215</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8753</v>
+        <v>3.718</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1064</v>
+        <v>2.9087</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7688</v>
+        <v>0.8093</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.8757</v>
+        <v>-3.9457</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2561</v>
+        <v>-1.9215</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6196</v>
+        <v>-2.0243</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0812</v>
+        <v>0.4891</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3236</v>
+        <v>0.2389</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.2502</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1097</v>
+        <v>-1.2735</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1089</v>
+        <v>-0.6642</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7329</v>
+        <v>-1.7135</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1408</v>
+        <v>-2.0397</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4079</v>
+        <v>0.3262</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8384</v>
@@ -1780,13 +1780,13 @@
         <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1409</v>
+        <v>0.1603</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2283</v>
+        <v>-0.1272</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3692</v>
+        <v>0.2875</v>
       </c>
       <c r="V17" t="n">
         <v>0.3321</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8314</v>
+        <v>-2.0723</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.143</v>
+        <v>-0.3069</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6884</v>
+        <v>-1.7654</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2277</v>
+        <v>-2.0004</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9872</v>
+        <v>-1.1497</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.215</v>
+        <v>-0.8508</v>
       </c>
       <c r="J18" t="n">
-        <v>3.718</v>
+        <v>1.8753</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9087</v>
+        <v>1.1064</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8093</v>
+        <v>0.7688</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.9457</v>
+        <v>-3.8757</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9215</v>
+        <v>-2.2561</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0243</v>
+        <v>-1.6196</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2559</v>
+        <v>1.2099</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2667</v>
+        <v>0.6158</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5226</v>
+        <v>0.5942</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2735</v>
+        <v>-0.1097</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>1.1089</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3343</v>
+        <v>-2.3538</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4174</v>
+        <v>-1.5185</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9169</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6033</v>
@@ -1936,13 +1936,13 @@
         <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.504</v>
+        <v>-0.5234</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0221</v>
+        <v>-0.079</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5261</v>
+        <v>-0.4444</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3991</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.247</v>
+        <v>-3.059</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.52</v>
+        <v>-2.1821</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.727</v>
+        <v>-0.8768</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3895</v>
+        <v>-2.1263</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.8747</v>
+        <v>-0.3732</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4852</v>
+        <v>-1.7531</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6865</v>
+        <v>-1.3073</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9814</v>
+        <v>0.0409</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2949</v>
+        <v>-1.3482</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.703</v>
+        <v>-0.819</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8933</v>
+        <v>-0.4142</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8097</v>
+        <v>-0.4049</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1496</v>
+        <v>0.044</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1432</v>
+        <v>0.1018</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2928</v>
+        <v>-0.0578</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.409</v>
+        <v>-3.5293</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5866</v>
+        <v>-1.8362</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8224</v>
+        <v>-1.6931</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1263</v>
+        <v>-2.1382</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3732</v>
+        <v>0.3431</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7531</v>
+        <v>-2.4812</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3073</v>
+        <v>0.2345</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0409</v>
+        <v>0.9619</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3482</v>
+        <v>-0.7274</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.819</v>
+        <v>-2.3727</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4142</v>
+        <v>-0.6188</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4049</v>
+        <v>-1.7538</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.306</v>
+        <v>-0.3363</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3026</v>
+        <v>-0.4298</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0033</v>
+        <v>0.0935</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6305</v>
+        <v>-3.6242</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9373</v>
+        <v>-1.9245</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6931</v>
+        <v>-1.6998</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1382</v>
+        <v>-2.3895</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3431</v>
+        <v>-2.8747</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4812</v>
+        <v>0.4852</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2345</v>
+        <v>-0.6865</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9619</v>
+        <v>-1.9814</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7274</v>
+        <v>1.2949</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3727</v>
+        <v>-1.703</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6188</v>
+        <v>-0.8933</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7538</v>
+        <v>-0.8097</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4374</v>
+        <v>-0.5269</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5309</v>
+        <v>-0.2613</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0935</v>
+        <v>-0.2656</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6642</v>
+        <v>-0.1219</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.956</v>
+        <v>-3.951</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.841</v>
+        <v>-3.2264</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.115</v>
+        <v>-0.7246</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.6341</v>
+        <v>-3.4344</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.9051</v>
+        <v>-2.5304</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.729</v>
+        <v>-0.9041</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8378</v>
+        <v>-1.9409</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9187</v>
+        <v>-1.9814</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7964</v>
+        <v>-1.4935</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9864</v>
+        <v>-0.549</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8099</v>
+        <v>-0.9445</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8381</v>
+        <v>-0.3212</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6962</v>
+        <v>-0.3088</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1419</v>
+        <v>-0.0124</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1338</v>
+        <v>-4.2982</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3275</v>
+        <v>-2.3466</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8063</v>
+        <v>-1.9516</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4344</v>
+        <v>-4.6341</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.5304</v>
+        <v>-3.9051</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9041</v>
+        <v>-0.729</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9409</v>
+        <v>-1.8378</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9814</v>
+        <v>-1.9187</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0405</v>
+        <v>0.0809</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4935</v>
+        <v>-2.7964</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.549</v>
+        <v>-1.9864</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9445</v>
+        <v>-0.8099</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.504</v>
+        <v>0.496</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4099</v>
+        <v>0.1906</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0941</v>
+        <v>0.3053</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8333</v>
+        <v>-6.6504</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0884</v>
+        <v>-1.9873</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.7449</v>
+        <v>-4.6632</v>
       </c>
       <c r="G25" t="n">
         <v>-3.3339</v>
@@ -2404,13 +2404,13 @@
         <v>0.3907</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1738</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1838</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2565</v>
+        <v>-0.1748</v>
       </c>
       <c r="V25" t="n">
         <v>-0.786</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.6825</v>
+        <v>-11.4064</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.078900000000001</v>
+        <v>-7.7756</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.6036</v>
+        <v>-3.6308</v>
       </c>
       <c r="G26" t="n">
         <v>-8.142099999999999</v>
@@ -2482,13 +2482,13 @@
         <v>2.5395</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1442</v>
+        <v>0.4203</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1048</v>
+        <v>0.4081</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0394</v>
+        <v>0.0122</v>
       </c>
       <c r="V26" t="n">
         <v>-1.3405</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-43.5525</v>
+        <v>-43.5526</v>
       </c>
       <c r="E27" t="n">
-        <v>-21.8012</v>
+        <v>-21.8014</v>
       </c>
       <c r="F27" t="n">
-        <v>-21.7513</v>
+        <v>-21.7512</v>
       </c>
       <c r="G27" t="n">
         <v>-32.78749999999999</v>
@@ -2536,10 +2536,10 @@
         <v>-1.148100000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.5023</v>
+        <v>-2.502300000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3541</v>
+        <v>1.354100000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-31.6397</v>
@@ -2560,13 +2560,13 @@
         <v>15.6275</v>
       </c>
       <c r="S27" t="n">
-        <v>1.623800000000001</v>
+        <v>1.6237</v>
       </c>
       <c r="T27" t="n">
-        <v>1.102</v>
+        <v>1.1019</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5218000000000002</v>
+        <v>0.5216999999999998</v>
       </c>
       <c r="V27" t="n">
         <v>-3.5981</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484329_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484329_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +653,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.41</v>
+        <v>7.803</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2852</v>
+        <v>3.6782</v>
       </c>
       <c r="F3" t="n">
         <v>4.1248</v>
       </c>
       <c r="G3" t="n">
-        <v>4.722</v>
+        <v>4.115</v>
       </c>
       <c r="H3" t="n">
         <v>4.3313</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3906</v>
+        <v>-0.2163</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8586</v>
+        <v>3.2516</v>
       </c>
       <c r="K3" t="n">
         <v>2.9279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9307</v>
+        <v>0.3237</v>
       </c>
       <c r="M3" t="n">
         <v>0.8633999999999999</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.441</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,11 +1379,16 @@
       <c r="X11" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0378</v>
+        <v>0.607</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3873</v>
+        <v>0.607</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6505</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.614</v>
+        <v>0.607</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0255</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0199</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0454</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. SERRA SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1867</v>
+        <v>-1.0378</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5209</v>
+        <v>-0.3873</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.6505</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6669</v>
+        <v>-0.614</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7222</v>
+        <v>-0.614</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9447</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.361</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1461</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.215</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.614</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4239</v>
+        <v>-0.614</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2702</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>-0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5764</v>
+        <v>0.0255</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0482</v>
+        <v>-0.0199</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6246</v>
+        <v>0.0454</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4959</v>
+        <v>0.3321</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,196 +1566,202 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>44.1578</v>
+        <v>-1.1867</v>
       </c>
       <c r="E14" t="n">
-        <v>22.3565</v>
+        <v>-0.5209</v>
       </c>
       <c r="F14" t="n">
-        <v>21.8012</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>32.7878</v>
+        <v>1.6669</v>
       </c>
       <c r="H14" t="n">
-        <v>19.2967</v>
+        <v>0.7222</v>
       </c>
       <c r="I14" t="n">
-        <v>13.4906</v>
+        <v>0.9447</v>
       </c>
       <c r="J14" t="n">
-        <v>31.6397</v>
+        <v>2.361</v>
       </c>
       <c r="K14" t="n">
-        <v>16.7945</v>
+        <v>1.1461</v>
       </c>
       <c r="L14" t="n">
-        <v>14.8451</v>
+        <v>1.215</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1478</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5023</v>
+        <v>-0.4239</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3541</v>
+        <v>-0.2702</v>
       </c>
       <c r="P14" t="n">
-        <v>8.790400000000002</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.6272</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>24.4179</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0184</v>
+        <v>-0.5764</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08369999999999997</v>
+        <v>0.0482</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1021</v>
+        <v>-0.6246</v>
       </c>
       <c r="V14" t="n">
-        <v>3.597899999999999</v>
+        <v>-1.4959</v>
       </c>
       <c r="W14" t="n">
-        <v>6.2605</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.6626</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7037</v>
+        <v>44.1578</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9799</v>
+        <v>22.3565</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2762</v>
+        <v>21.8012</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9192</v>
+        <v>32.7878</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0811</v>
+        <v>19.2967</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1619</v>
+        <v>13.4907</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2358</v>
+        <v>31.63969999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4543</v>
+        <v>16.7945</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7815</v>
+        <v>14.8451</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.1551</v>
+        <v>1.1478</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.5354</v>
+        <v>2.5023</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6196</v>
+        <v>-1.3541</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.586</v>
+        <v>8.790400000000002</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-15.6272</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3441</v>
+        <v>24.4179</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5029</v>
+        <v>-1.0184</v>
       </c>
       <c r="T15" t="n">
-        <v>0.569</v>
+        <v>0.08369999999999997</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-1.1021</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7061</v>
+        <v>3.597899999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1052</v>
+        <v>6.2605</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3991</v>
-      </c>
+        <v>-2.6626</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5982</v>
+        <v>0.3967</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3625</v>
+        <v>2.6729</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9607</v>
+        <v>-2.2762</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2277</v>
+        <v>-1.2262</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9872</v>
+        <v>-1.3881</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.215</v>
+        <v>0.1619</v>
       </c>
       <c r="J16" t="n">
-        <v>3.718</v>
+        <v>2.9288</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9087</v>
+        <v>1.1474</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8093</v>
+        <v>1.7815</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.9457</v>
+        <v>-4.1551</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9215</v>
+        <v>-2.5354</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0243</v>
+        <v>-1.6196</v>
       </c>
       <c r="P16" t="n">
         <v>-0.586</v>
@@ -1702,881 +1773,1103 @@
         <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4891</v>
+        <v>0.5029</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2389</v>
+        <v>0.569</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2502</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2735</v>
+        <v>1.7061</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6642</v>
+        <v>2.1052</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7135</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0397</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3262</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8384</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1059</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9443</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0409</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0409</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8793</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9443</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1603</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1272</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2875</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0723</v>
+        <v>-1.5982</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3069</v>
+        <v>0.3625</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7654</v>
+        <v>-1.9607</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0004</v>
+        <v>-0.2277</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1497</v>
+        <v>0.9872</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8508</v>
+        <v>-1.215</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8753</v>
+        <v>3.718</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1064</v>
+        <v>2.9087</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7688</v>
+        <v>0.8093</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.8757</v>
+        <v>-3.9457</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2561</v>
+        <v>-1.9215</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6196</v>
+        <v>-2.0243</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2099</v>
+        <v>0.4891</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6158</v>
+        <v>0.2389</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5942</v>
+        <v>0.2502</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1097</v>
+        <v>-1.2735</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1089</v>
+        <v>-0.6642</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3538</v>
+        <v>-1.7135</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5185</v>
+        <v>-2.0397</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8352000000000001</v>
+        <v>0.3262</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6033</v>
+        <v>-0.8384</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8998</v>
+        <v>0.1059</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2965</v>
+        <v>-0.9443</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4395</v>
+        <v>0.0409</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1413</v>
+        <v>0.0409</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7017</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1638</v>
+        <v>-0.8793</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7585</v>
+        <v>0.065</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4052</v>
+        <v>-0.9443</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5234</v>
+        <v>0.1603</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.079</v>
+        <v>-0.1272</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4444</v>
+        <v>0.2875</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3991</v>
+        <v>0.3321</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3991</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.059</v>
+        <v>-2.0723</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1821</v>
+        <v>-0.3069</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8768</v>
+        <v>-1.7654</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1263</v>
+        <v>-2.0004</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3732</v>
+        <v>-1.1497</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7531</v>
+        <v>-0.8508</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3073</v>
+        <v>1.8753</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0409</v>
+        <v>1.1064</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3482</v>
+        <v>0.7688</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.819</v>
+        <v>-3.8757</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4142</v>
+        <v>-2.2561</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4049</v>
+        <v>-1.6196</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.7348</v>
       </c>
       <c r="S20" t="n">
-        <v>0.044</v>
+        <v>1.2099</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1018</v>
+        <v>0.6158</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0578</v>
+        <v>0.5942</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1097</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5293</v>
+        <v>-2.3538</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8362</v>
+        <v>-1.5185</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6931</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1382</v>
+        <v>-2.6033</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3431</v>
+        <v>-2.8998</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4812</v>
+        <v>0.2965</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2345</v>
+        <v>-1.4395</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9619</v>
+        <v>-2.1413</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7274</v>
+        <v>0.7017</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3727</v>
+        <v>-1.1638</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6188</v>
+        <v>-0.7585</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7538</v>
+        <v>-0.4052</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3363</v>
+        <v>-0.5234</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4298</v>
+        <v>-0.079</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0935</v>
+        <v>-0.4444</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6642</v>
+        <v>-0.3991</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6242</v>
+        <v>-3.059</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9245</v>
+        <v>-2.1821</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6998</v>
+        <v>-0.8768</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3895</v>
+        <v>-2.1263</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8747</v>
+        <v>-0.3732</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4852</v>
+        <v>-1.7531</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6865</v>
+        <v>-1.3073</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9814</v>
+        <v>0.0409</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2949</v>
+        <v>-1.3482</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.703</v>
+        <v>-0.819</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8933</v>
+        <v>-0.4142</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8097</v>
+        <v>-0.4049</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5269</v>
+        <v>0.044</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2613</v>
+        <v>0.1018</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2656</v>
+        <v>-0.0578</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>P. MARTINEZ SERRANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.951</v>
+        <v>-3.5293</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2264</v>
+        <v>-1.8362</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7246</v>
+        <v>-1.6931</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4344</v>
+        <v>-2.1382</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5304</v>
+        <v>0.3431</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9041</v>
+        <v>-2.4812</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9409</v>
+        <v>0.2345</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9814</v>
+        <v>0.9619</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0405</v>
+        <v>-0.7274</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4935</v>
+        <v>-2.3727</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.549</v>
+        <v>-0.6188</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9445</v>
+        <v>-1.7538</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3212</v>
+        <v>-0.3363</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3088</v>
+        <v>-0.4298</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0124</v>
+        <v>0.0935</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2982</v>
+        <v>-3.6242</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3466</v>
+        <v>-1.9245</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9516</v>
+        <v>-1.6998</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6341</v>
+        <v>-2.3895</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.9051</v>
+        <v>-2.8747</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.729</v>
+        <v>0.4852</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8378</v>
+        <v>-0.6865</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9187</v>
+        <v>-1.9814</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0809</v>
+        <v>1.2949</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7964</v>
+        <v>-1.703</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.9864</v>
+        <v>-0.8933</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8099</v>
+        <v>-0.8097</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S24" t="n">
-        <v>0.496</v>
+        <v>-0.5269</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1906</v>
+        <v>-0.2613</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3053</v>
+        <v>-0.2656</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9414</v>
+        <v>-0.1219</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6504</v>
+        <v>-3.951</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9873</v>
+        <v>-3.2264</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.6632</v>
+        <v>-0.7246</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.3339</v>
+        <v>-3.4344</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6202</v>
+        <v>-2.5304</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7138</v>
+        <v>-0.9041</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5367</v>
+        <v>-1.9409</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4963</v>
+        <v>-1.9814</v>
       </c>
       <c r="L25" t="n">
         <v>0.0405</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.8707</v>
+        <v>-1.4935</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.1164</v>
+        <v>-0.549</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7542</v>
+        <v>-0.9445</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.5395</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S25" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.3212</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1838</v>
+        <v>-0.3088</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1748</v>
+        <v>-0.0124</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.786</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0084</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.4064</v>
+        <v>-4.2982</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.7756</v>
+        <v>-2.3466</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.6308</v>
+        <v>-1.9516</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.142099999999999</v>
+        <v>-4.6341</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.2989</v>
+        <v>-3.9051</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.8433</v>
+        <v>-0.729</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.5773</v>
+        <v>-1.8378</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.4889</v>
+        <v>-1.9187</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.0884</v>
+        <v>0.0809</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.5648</v>
+        <v>-2.7964</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.8099</v>
+        <v>-1.9864</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.7548</v>
+        <v>-0.8099</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R26" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4203</v>
+        <v>0.496</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4081</v>
+        <v>0.1906</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0122</v>
+        <v>0.3053</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.3405</v>
+        <v>-0.9414</v>
       </c>
       <c r="W26" t="n">
         <v>0.2772</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.6177</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
+        <v>-6.6504</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.9873</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-4.6632</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.3339</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.6202</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.7138</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-3.8707</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-2.1164</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.7542</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-2.5395</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.1838</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1748</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.786</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.0084</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R. FERNANDEZ DIAZ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-11.4064</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-7.7756</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-3.6308</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-8.142099999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-4.2989</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-3.8433</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-3.5773</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.4889</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-2.0884</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-4.5648</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-2.8099</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-1.7548</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.3405</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.6177</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484329_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>-43.5526</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E29" t="n">
         <v>-21.8014</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F29" t="n">
         <v>-21.7512</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G29" t="n">
         <v>-32.78749999999999</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H29" t="n">
         <v>-19.2969</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I29" t="n">
         <v>-13.491</v>
       </c>
-      <c r="J27" t="n">
-        <v>-1.148100000000001</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-2.502300000000001</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.354100000000001</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="J29" t="n">
+        <v>-1.1481</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-2.5022</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.3541</v>
+      </c>
+      <c r="M29" t="n">
         <v>-31.6397</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N29" t="n">
         <v>-16.7945</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O29" t="n">
         <v>-14.8448</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P29" t="n">
         <v>-8.790299999999998</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q29" t="n">
         <v>-24.4177</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R29" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S29" t="n">
         <v>1.6237</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T29" t="n">
         <v>1.1019</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U29" t="n">
         <v>0.5216999999999998</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V29" t="n">
         <v>-3.5981</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W29" t="n">
         <v>2.6625</v>
       </c>
-      <c r="X27" t="n">
+      <c r="X29" t="n">
         <v>-6.260599999999999</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
